--- a/artfynd/A 49422-2023 artfynd.xlsx
+++ b/artfynd/A 49422-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49422-2023 artfynd.xlsx
+++ b/artfynd/A 49422-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113886928</v>
+        <v>113887374</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>827817</v>
+        <v>827821</v>
       </c>
       <c r="R2" t="n">
-        <v>7397600</v>
+        <v>7397602</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113887357</v>
+        <v>113888803</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +823,7 @@
         <v>827821</v>
       </c>
       <c r="R3" t="n">
-        <v>7397602</v>
+        <v>7397600</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113887658</v>
+        <v>113887357</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>827787</v>
+        <v>827821</v>
       </c>
       <c r="R4" t="n">
-        <v>7397608</v>
+        <v>7397602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113888803</v>
+        <v>113886928</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,7 +1032,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>827821</v>
+        <v>827817</v>
       </c>
       <c r="R5" t="n">
         <v>7397600</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113887397</v>
+        <v>113887658</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>827817</v>
+        <v>827787</v>
       </c>
       <c r="R6" t="n">
-        <v>7397600</v>
+        <v>7397608</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113887374</v>
+        <v>113887397</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>827821</v>
+        <v>827817</v>
       </c>
       <c r="R7" t="n">
-        <v>7397602</v>
+        <v>7397600</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 49422-2023 artfynd.xlsx
+++ b/artfynd/A 49422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887374</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887357</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886928</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>